--- a/задолженность.xlsx
+++ b/задолженность.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Данные" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Данные'!$A$1:$G$101</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Данные'!$A$1:$G$104</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G101"/>
+  <dimension ref="A1:G104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -489,14 +489,14 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>ДЗ</t>
+          <t>ПДЗ</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>954</v>
       </c>
       <c r="G2" t="n">
-        <v>537</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -510,7 +510,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>К/а 2</t>
+          <t>К/а 1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -520,14 +520,14 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>ПДЗ</t>
+          <t>ДЗ</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>191</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>214</v>
       </c>
     </row>
     <row r="4">
@@ -541,7 +541,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>К/а 3</t>
+          <t>К/а 2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -551,11 +551,11 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>ДЗ</t>
+          <t>ПДЗ</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>765</v>
+        <v>325</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -572,7 +572,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>К/а 4</t>
+          <t>К/а 2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -589,7 +589,7 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>374</v>
+        <v>381</v>
       </c>
     </row>
     <row r="6">
@@ -603,7 +603,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>К/а 5</t>
+          <t>К/а 3</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>294</v>
+        <v>550</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -634,7 +634,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>К/а 6</t>
+          <t>К/а 3</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -648,10 +648,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>328</v>
       </c>
     </row>
     <row r="8">
@@ -665,7 +665,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>К/а 7</t>
+          <t>К/а 4</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -682,7 +682,7 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>52</v>
+        <v>192</v>
       </c>
     </row>
     <row r="9">
@@ -696,7 +696,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>К/а 8</t>
+          <t>К/а 5</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -710,7 +710,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>759</v>
+        <v>854</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -727,7 +727,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>К/а 9</t>
+          <t>К/а 6</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>586</v>
+        <v>154</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -758,7 +758,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>К/а 10</t>
+          <t>К/а 7</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -775,7 +775,7 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>170</v>
+        <v>742</v>
       </c>
     </row>
     <row r="12">
@@ -784,12 +784,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ДО2</t>
+          <t>ДО1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>К/а 1</t>
+          <t>К/а 8</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -803,7 +803,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>954</v>
+        <v>858</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -815,12 +815,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ДО2</t>
+          <t>ДО1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>К/а 2</t>
+          <t>К/а 9</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ДО2</t>
+          <t>ДО1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>К/а 3</t>
+          <t>К/а 10</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -868,7 +868,7 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>563</v>
+        <v>139</v>
       </c>
     </row>
     <row r="15">
@@ -882,7 +882,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>К/а 4</t>
+          <t>К/а 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -896,7 +896,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>511</v>
+        <v>704</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -913,7 +913,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>К/а 5</t>
+          <t>К/а 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>224</v>
+        <v>482</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -944,7 +944,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>К/а 6</t>
+          <t>К/а 3</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -961,7 +961,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>146</v>
+        <v>82</v>
       </c>
     </row>
     <row r="18">
@@ -975,7 +975,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>К/а 7</t>
+          <t>К/а 4</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -989,7 +989,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>979</v>
+        <v>130</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>К/а 8</t>
+          <t>К/а 5</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>642</v>
+        <v>145</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -1037,7 +1037,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>К/а 9</t>
+          <t>К/а 6</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1054,7 +1054,7 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>406</v>
+        <v>273</v>
       </c>
     </row>
     <row r="21">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>К/а 10</t>
+          <t>К/а 7</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1082,7 +1082,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>562</v>
+        <v>338</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -1094,12 +1094,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ДО3</t>
+          <t>ДО2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>К/а 1</t>
+          <t>К/а 8</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1113,7 +1113,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>683</v>
+        <v>567</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1125,12 +1125,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ДО3</t>
+          <t>ДО2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>К/а 2</t>
+          <t>К/а 9</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1147,7 +1147,7 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>700</v>
+        <v>666</v>
       </c>
     </row>
     <row r="24">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ДО3</t>
+          <t>ДО2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>К/а 3</t>
+          <t>К/а 10</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1175,7 +1175,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>862</v>
+        <v>127</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>К/а 4</t>
+          <t>К/а 1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1206,7 +1206,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>394</v>
+        <v>624</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>К/а 5</t>
+          <t>К/а 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1240,7 +1240,7 @@
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>529</v>
+        <v>253</v>
       </c>
     </row>
     <row r="27">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>К/а 6</t>
+          <t>К/а 3</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1268,7 +1268,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>559</v>
+        <v>833</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>К/а 7</t>
+          <t>К/а 4</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1299,7 +1299,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>421</v>
+        <v>715</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1316,7 +1316,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>К/а 8</t>
+          <t>К/а 5</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1333,7 +1333,7 @@
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>348</v>
+        <v>768</v>
       </c>
     </row>
     <row r="30">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>К/а 9</t>
+          <t>К/а 6</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>950</v>
+        <v>658</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>К/а 10</t>
+          <t>К/а 7</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1392,7 +1392,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>457</v>
+        <v>479</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1404,12 +1404,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>ДО4</t>
+          <t>ДО3</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>К/а 1</t>
+          <t>К/а 8</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1426,7 +1426,7 @@
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>651</v>
+        <v>275</v>
       </c>
     </row>
     <row r="33">
@@ -1435,12 +1435,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ДО4</t>
+          <t>ДО3</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>К/а 2</t>
+          <t>К/а 9</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1454,7 +1454,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>375</v>
+        <v>559</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ДО4</t>
+          <t>ДО3</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>К/а 3</t>
+          <t>К/а 10</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>477</v>
+        <v>653</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>К/а 4</t>
+          <t>К/а 1</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1519,7 +1519,7 @@
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>156</v>
+        <v>334</v>
       </c>
     </row>
     <row r="36">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>К/а 5</t>
+          <t>К/а 2</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1547,7 +1547,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>306</v>
+        <v>928</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>К/а 6</t>
+          <t>К/а 3</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1578,7 +1578,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>281</v>
+        <v>56</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1595,7 +1595,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>К/а 7</t>
+          <t>К/а 4</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1612,7 +1612,7 @@
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>449</v>
+        <v>213</v>
       </c>
     </row>
     <row r="39">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>К/а 8</t>
+          <t>К/а 5</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1640,7 +1640,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>629</v>
+        <v>814</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1657,7 +1657,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>К/а 9</t>
+          <t>К/а 6</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1671,7 +1671,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>255</v>
+        <v>482</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1688,7 +1688,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>К/а 10</t>
+          <t>К/а 7</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1705,7 +1705,7 @@
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>411</v>
+        <v>398</v>
       </c>
     </row>
     <row r="42">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>ДО5</t>
+          <t>ДО4</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>К/а 1</t>
+          <t>К/а 8</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1733,7 +1733,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>521</v>
+        <v>384</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1745,12 +1745,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ДО5</t>
+          <t>ДО4</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>К/а 2</t>
+          <t>К/а 9</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1764,7 +1764,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>790</v>
+        <v>209</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1776,12 +1776,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ДО5</t>
+          <t>ДО4</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>К/а 3</t>
+          <t>К/а 10</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1798,7 +1798,7 @@
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>474</v>
+        <v>270</v>
       </c>
     </row>
     <row r="45">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>К/а 4</t>
+          <t>К/а 1</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1826,7 +1826,7 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>693</v>
+        <v>881</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>К/а 5</t>
+          <t>К/а 2</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1857,7 +1857,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>286</v>
+        <v>394</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>К/а 6</t>
+          <t>К/а 3</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1891,7 +1891,7 @@
         <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>744</v>
+        <v>154</v>
       </c>
     </row>
     <row r="48">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>К/а 7</t>
+          <t>К/а 4</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1919,7 +1919,7 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>306</v>
+        <v>194</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>К/а 8</t>
+          <t>К/а 5</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1950,7 +1950,7 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>770</v>
+        <v>439</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1967,7 +1967,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>К/а 9</t>
+          <t>К/а 6</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1984,7 +1984,7 @@
         <v>0</v>
       </c>
       <c r="G50" t="n">
-        <v>394</v>
+        <v>149</v>
       </c>
     </row>
     <row r="51">
@@ -1998,7 +1998,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>К/а 10</t>
+          <t>К/а 7</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2012,7 +2012,7 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>944</v>
+        <v>467</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -2024,12 +2024,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>ДО6</t>
+          <t>ДО5</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>К/а 1</t>
+          <t>К/а 8</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2043,7 +2043,7 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>315</v>
+        <v>402</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -2055,12 +2055,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ДО6</t>
+          <t>ДО5</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>К/а 2</t>
+          <t>К/а 9</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2077,7 +2077,7 @@
         <v>0</v>
       </c>
       <c r="G53" t="n">
-        <v>117</v>
+        <v>668</v>
       </c>
     </row>
     <row r="54">
@@ -2086,12 +2086,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ДО6</t>
+          <t>ДО5</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>К/а 3</t>
+          <t>К/а 10</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2105,7 +2105,7 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -2122,7 +2122,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>К/а 4</t>
+          <t>К/а 1</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2136,7 +2136,7 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>631</v>
+        <v>94</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -2153,7 +2153,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>К/а 5</t>
+          <t>К/а 2</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2170,7 +2170,7 @@
         <v>0</v>
       </c>
       <c r="G56" t="n">
-        <v>540</v>
+        <v>797</v>
       </c>
     </row>
     <row r="57">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>К/а 6</t>
+          <t>К/а 3</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>161</v>
+        <v>570</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -2215,7 +2215,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>К/а 7</t>
+          <t>К/а 4</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -2229,7 +2229,7 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>86</v>
+        <v>599</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -2246,7 +2246,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>К/а 8</t>
+          <t>К/а 5</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2263,7 +2263,7 @@
         <v>0</v>
       </c>
       <c r="G59" t="n">
-        <v>800</v>
+        <v>177</v>
       </c>
     </row>
     <row r="60">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>К/а 9</t>
+          <t>К/а 6</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>891</v>
+        <v>487</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2308,7 +2308,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>К/а 10</t>
+          <t>К/а 7</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2322,7 +2322,7 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>463</v>
+        <v>130</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2334,12 +2334,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>ДО7</t>
+          <t>ДО6</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>К/а 1</t>
+          <t>К/а 8</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2356,7 +2356,7 @@
         <v>0</v>
       </c>
       <c r="G62" t="n">
-        <v>481</v>
+        <v>615</v>
       </c>
     </row>
     <row r="63">
@@ -2365,12 +2365,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>ДО7</t>
+          <t>ДО6</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>К/а 2</t>
+          <t>К/а 9</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2384,7 +2384,7 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>595</v>
+        <v>400</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2396,12 +2396,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>ДО7</t>
+          <t>ДО6</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>К/а 3</t>
+          <t>К/а 10</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2415,7 +2415,7 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>255</v>
+        <v>693</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>К/а 4</t>
+          <t>К/а 1</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -2449,7 +2449,7 @@
         <v>0</v>
       </c>
       <c r="G65" t="n">
-        <v>54</v>
+        <v>683</v>
       </c>
     </row>
     <row r="66">
@@ -2463,7 +2463,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>К/а 5</t>
+          <t>К/а 2</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2477,7 +2477,7 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>608</v>
+        <v>982</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2494,7 +2494,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>К/а 6</t>
+          <t>К/а 3</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -2508,7 +2508,7 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>188</v>
+        <v>420</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2525,7 +2525,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>К/а 7</t>
+          <t>К/а 4</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -2542,7 +2542,7 @@
         <v>0</v>
       </c>
       <c r="G68" t="n">
-        <v>644</v>
+        <v>641</v>
       </c>
     </row>
     <row r="69">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>К/а 8</t>
+          <t>К/а 5</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -2570,7 +2570,7 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>943</v>
+        <v>296</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2587,7 +2587,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>К/а 9</t>
+          <t>К/а 6</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -2601,7 +2601,7 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>414</v>
+        <v>771</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>К/а 10</t>
+          <t>К/а 7</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -2635,7 +2635,7 @@
         <v>0</v>
       </c>
       <c r="G71" t="n">
-        <v>660</v>
+        <v>121</v>
       </c>
     </row>
     <row r="72">
@@ -2644,12 +2644,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>ДО8</t>
+          <t>ДО7</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>К/а 1</t>
+          <t>К/а 8</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2663,7 +2663,7 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>962</v>
+        <v>146</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2675,12 +2675,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>ДО8</t>
+          <t>ДО7</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>К/а 2</t>
+          <t>К/а 9</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2694,7 +2694,7 @@
         </is>
       </c>
       <c r="F73" t="n">
-        <v>216</v>
+        <v>727</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2706,12 +2706,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>ДО8</t>
+          <t>ДО7</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>К/а 3</t>
+          <t>К/а 10</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2728,7 +2728,7 @@
         <v>0</v>
       </c>
       <c r="G74" t="n">
-        <v>100</v>
+        <v>283</v>
       </c>
     </row>
     <row r="75">
@@ -2742,7 +2742,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>К/а 4</t>
+          <t>К/а 1</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -2756,7 +2756,7 @@
         </is>
       </c>
       <c r="F75" t="n">
-        <v>488</v>
+        <v>891</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2773,7 +2773,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>К/а 5</t>
+          <t>К/а 2</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2787,7 +2787,7 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>780</v>
+        <v>346</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2804,7 +2804,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>К/а 6</t>
+          <t>К/а 3</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2821,7 +2821,7 @@
         <v>0</v>
       </c>
       <c r="G77" t="n">
-        <v>540</v>
+        <v>131</v>
       </c>
     </row>
     <row r="78">
@@ -2835,7 +2835,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>К/а 7</t>
+          <t>К/а 4</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -2849,7 +2849,7 @@
         </is>
       </c>
       <c r="F78" t="n">
-        <v>875</v>
+        <v>975</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2866,7 +2866,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>К/а 8</t>
+          <t>К/а 5</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -2880,7 +2880,7 @@
         </is>
       </c>
       <c r="F79" t="n">
-        <v>121</v>
+        <v>288</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2897,7 +2897,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>К/а 9</t>
+          <t>К/а 6</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -2914,7 +2914,7 @@
         <v>0</v>
       </c>
       <c r="G80" t="n">
-        <v>284</v>
+        <v>153</v>
       </c>
     </row>
     <row r="81">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>К/а 10</t>
+          <t>К/а 7</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -2942,7 +2942,7 @@
         </is>
       </c>
       <c r="F81" t="n">
-        <v>731</v>
+        <v>489</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2954,12 +2954,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>ДО9</t>
+          <t>ДО8</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>К/а 1</t>
+          <t>К/а 8</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -2973,7 +2973,7 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>464</v>
+        <v>334</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2985,12 +2985,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>ДО9</t>
+          <t>ДО8</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>К/а 2</t>
+          <t>К/а 9</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -3007,7 +3007,7 @@
         <v>0</v>
       </c>
       <c r="G83" t="n">
-        <v>584</v>
+        <v>514</v>
       </c>
     </row>
     <row r="84">
@@ -3016,12 +3016,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>ДО9</t>
+          <t>ДО8</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>К/а 3</t>
+          <t>К/а 10</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>538</v>
+        <v>750</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -3052,7 +3052,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>К/а 4</t>
+          <t>К/а 1</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -3066,7 +3066,7 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>452</v>
+        <v>423</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -3083,7 +3083,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>К/а 5</t>
+          <t>К/а 2</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -3100,7 +3100,7 @@
         <v>0</v>
       </c>
       <c r="G86" t="n">
-        <v>272</v>
+        <v>216</v>
       </c>
     </row>
     <row r="87">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>К/а 6</t>
+          <t>К/а 3</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -3128,7 +3128,7 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>787</v>
+        <v>479</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -3145,7 +3145,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>К/а 7</t>
+          <t>К/а 4</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -3159,7 +3159,7 @@
         </is>
       </c>
       <c r="F88" t="n">
-        <v>120</v>
+        <v>413</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -3176,7 +3176,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>К/а 8</t>
+          <t>К/а 5</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -3193,7 +3193,7 @@
         <v>0</v>
       </c>
       <c r="G89" t="n">
-        <v>374</v>
+        <v>264</v>
       </c>
     </row>
     <row r="90">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>К/а 9</t>
+          <t>К/а 6</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -3221,7 +3221,7 @@
         </is>
       </c>
       <c r="F90" t="n">
-        <v>133</v>
+        <v>786</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -3238,7 +3238,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>К/а 10</t>
+          <t>К/а 7</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -3252,7 +3252,7 @@
         </is>
       </c>
       <c r="F91" t="n">
-        <v>521</v>
+        <v>323</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -3264,12 +3264,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>ДО10</t>
+          <t>ДО9</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>К/а 1</t>
+          <t>К/а 8</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -3286,7 +3286,7 @@
         <v>0</v>
       </c>
       <c r="G92" t="n">
-        <v>651</v>
+        <v>768</v>
       </c>
     </row>
     <row r="93">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>ДО10</t>
+          <t>ДО9</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>К/а 2</t>
+          <t>К/а 9</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="F93" t="n">
-        <v>286</v>
+        <v>799</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -3326,12 +3326,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>ДО10</t>
+          <t>ДО9</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>К/а 3</t>
+          <t>К/а 10</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -3345,7 +3345,7 @@
         </is>
       </c>
       <c r="F94" t="n">
-        <v>190</v>
+        <v>713</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -3362,7 +3362,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>К/а 4</t>
+          <t>К/а 1</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -3379,7 +3379,7 @@
         <v>0</v>
       </c>
       <c r="G95" t="n">
-        <v>73</v>
+        <v>123</v>
       </c>
     </row>
     <row r="96">
@@ -3393,7 +3393,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>К/а 5</t>
+          <t>К/а 2</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -3407,7 +3407,7 @@
         </is>
       </c>
       <c r="F96" t="n">
-        <v>294</v>
+        <v>723</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -3424,7 +3424,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>К/а 6</t>
+          <t>К/а 3</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -3438,7 +3438,7 @@
         </is>
       </c>
       <c r="F97" t="n">
-        <v>485</v>
+        <v>700</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -3455,7 +3455,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>К/а 7</t>
+          <t>К/а 4</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -3472,7 +3472,7 @@
         <v>0</v>
       </c>
       <c r="G98" t="n">
-        <v>662</v>
+        <v>225</v>
       </c>
     </row>
     <row r="99">
@@ -3486,7 +3486,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>К/а 8</t>
+          <t>К/а 5</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -3500,7 +3500,7 @@
         </is>
       </c>
       <c r="F99" t="n">
-        <v>338</v>
+        <v>646</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3517,7 +3517,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>К/а 9</t>
+          <t>К/а 6</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -3531,7 +3531,7 @@
         </is>
       </c>
       <c r="F100" t="n">
-        <v>601</v>
+        <v>796</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3548,28 +3548,121 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
+          <t>К/а 7</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>ДД100</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>ДЗ</t>
+        </is>
+      </c>
+      <c r="F101" t="n">
+        <v>0</v>
+      </c>
+      <c r="G101" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>ДО10</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>К/а 8</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>ДД101</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>ПДЗ</t>
+        </is>
+      </c>
+      <c r="F102" t="n">
+        <v>267</v>
+      </c>
+      <c r="G102" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>ДО10</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>К/а 9</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>ДД102</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>ДЗ</t>
+        </is>
+      </c>
+      <c r="F103" t="n">
+        <v>523</v>
+      </c>
+      <c r="G103" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>ДО10</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
           <t>К/а 10</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>ДД100</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>ДЗ</t>
-        </is>
-      </c>
-      <c r="F101" t="n">
-        <v>0</v>
-      </c>
-      <c r="G101" t="n">
-        <v>459</v>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>ДД103</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>ДЗ</t>
+        </is>
+      </c>
+      <c r="F104" t="n">
+        <v>0</v>
+      </c>
+      <c r="G104" t="n">
+        <v>438</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G101"/>
+  <autoFilter ref="A1:G104"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>